--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_追加データ依頼票_見込量算定_20260914.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_追加データ依頼票_見込量算定_20260914.xlsx
@@ -1706,14 +1706,14 @@
           <t>需要量と供給可能量を分けて示す</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>一部対応</t>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>対応</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>見える化のＤ25〜Ｄ29（定員）は取得済み。**事業所別の定員・稼働率・待機者数（依頼票H15）が未受領のため、見込量と定員の突合ができていない。**5年間を通じて実績0のサービスが6区分あり、区域内に事業所がないのか需要がないのかを分けられていない</t>
+          <t>**見える化のＤ25〜Ｄ27（定員・令和7年度）と令和11年度の見込量を突き合わせた（回数日数ベース見込量 06_定員との突合）。**介護老人福祉施設は定員54人に対し67.6人/月で125.1％となり、13.6人が町外の施設の利用にあたる。介護老人保健施設・介護医療院・特定施設入居者生活介護・通所リハビリテーションは町内に事業所がなく、実績はすべて町外の利用である。**小規模多機能型居宅介護は見込み31.3人/月で、登録定員の上限29人を超える可能性がある。**事業所別の稼働率・待機者数（依頼票H15）は引き続き未受領</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">

--- a/小野町_引継ぎ_整理済/16_町データ依頼/小野町_追加データ依頼票_見込量算定_20260914.xlsx
+++ b/小野町_引継ぎ_整理済/16_町データ依頼/小野町_追加データ依頼票_見込量算定_20260914.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>**1ptで月額295円規模**</t>
+          <t>**1ptで月額290円規模**</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>地域支援事業費の実績と事業別内訳（**依頼票S6**）。年報 様式4の令和6・7年度が未入力</t>
+          <t>地域支援事業費の**事業別内訳**（**依頼票S6**）。総額は年報 様式4 で令和3〜6年度が取れたが、様式4は3科目の合計しか持たない。年報 様式4の令和6・7年度が未入力</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1％で月額4.0円。3年計で約207,000千円の規模</t>
+          <t>1％で月額3.7円。3年計で約207,000千円の規模</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>**1ptで月額303円**</t>
+          <t>**1ptで月額297円**</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1％で月額63円。±1.5％を感度分析に併記済み</t>
+          <t>1％で月額62円。±1.5％を感度分析に併記済み</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="C2" s="7" t="n">
-        <v>3330495.076051343</v>
+        <v>3280603.661724661</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>207260</v>
+        <v>191748.708</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>**第9期計画の見込額を仮置き。実績未受領（依頼票S6）**</t>
+          <t>**年報 様式4 の令和6年度決算（63,916千円）を3年度とも据え置いた。事業別の内訳は様式4になく未受領（依頼票S6）**</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>110960</v>
+        <v>103743.141</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>6682.45299339857</v>
+        <v>6558.377219671416</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>6579.719224350069</v>
+        <v>6455.643450622917</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>6382.812833673778</v>
+        <v>6258.737059946626</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>302.8724274443475</v>
+        <v>297.273205338588</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>-294.6280424782062</v>
+        <v>-289.7389190092872</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>-85.61147420708312</v>
+        <v>-85.61147420708221</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>62.83489103094689</v>
+        <v>61.89361307946547</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>3.989638903040941</v>
+        <v>3.690159117247276</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>62.83489103094689</v>
+        <v>61.89361307946547</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
